--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.24039282063157</v>
+        <v>6.701563833352631</v>
       </c>
       <c r="D2" t="n">
-        <v>41.44357172334701</v>
+        <v>6.73458040504389</v>
       </c>
       <c r="E2" t="n">
-        <v>14.7042364479353</v>
+        <v>2.389438422789486</v>
       </c>
       <c r="F2" t="n">
-        <v>14.95589281958982</v>
+        <v>2.430332583183346</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.41798625135591</v>
+        <v>9.817922765845335</v>
       </c>
       <c r="D3" t="n">
-        <v>60.44741429715547</v>
+        <v>9.822704823287763</v>
       </c>
       <c r="E3" t="n">
-        <v>14.7042364479353</v>
+        <v>2.389438422789486</v>
       </c>
       <c r="F3" t="n">
-        <v>14.95589281958982</v>
+        <v>2.430332583183346</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.15243979699613</v>
+        <v>9.449771467011873</v>
       </c>
       <c r="D4" t="n">
-        <v>58.12795285708918</v>
+        <v>9.445792339276993</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7042364479353</v>
+        <v>2.389438422789486</v>
       </c>
       <c r="F4" t="n">
-        <v>14.95589281958982</v>
+        <v>2.430332583183346</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.93963133179935</v>
+        <v>3.890190091417394</v>
       </c>
       <c r="D5" t="n">
-        <v>23.23427392136523</v>
+        <v>3.775569512221849</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7042364479353</v>
+        <v>2.389438422789486</v>
       </c>
       <c r="F5" t="n">
-        <v>14.95589281958982</v>
+        <v>2.430332583183346</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
